--- a/Server/NewServer/bin/commonconfig/setting/guild_dungeon.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/guild_dungeon.xlsx
@@ -32,7 +32,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -43,7 +43,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-推荐人数</t>
+Recommended player count</t>
         </r>
       </text>
     </comment>
@@ -58,7 +58,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-面板奖励展示</t>
+Reward display on the panel</t>
         </r>
       </text>
     </comment>
